--- a/results/Int Task Remove ACC -0.2/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.2/Linea_fi_all.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.01443202979515833 +/- 0.002302783588026012</t>
+          <t>0.014400993171942943 +/- 0.002260352756801142</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0010862818125388363 +/- 0.0005052396212321451</t>
+          <t>0.0010552451893234504 +/- 0.0005042854379041572</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
+          <t>0.0005896958410925191 +/- 0.000489749653571065</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
           <t>0.0005586592178771332 +/- 0.0004561433413004218</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.0005896958410925191 +/- 0.000489749653571065</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.08595758354755785 +/- 0.002892923312737976</t>
+          <t>0.0859897172236504 +/- 0.0029034336755980653</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.045147814910025695 +/- 0.0037891858625385914</t>
+          <t>0.04517994858611825 +/- 0.003829708718621996</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.024590163934426257 +/- 0.0037794844153985555</t>
+          <t>0.024558019929283213 +/- 0.003751909086831229</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.028672452587592445 +/- 0.0024973223528839713</t>
+          <t>0.028704596592735488 +/- 0.002583746250608636</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.006557377049180369 +/- 0.0023054221892691963</t>
+          <t>0.006621665059466442 +/- 0.002305422189269193</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.19577194106342083 +/- 0.005809498551571881</t>
+          <t>0.1957399103139013 +/- 0.00580711393551191</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.08231902626521458 +/- 0.006492056917441765</t>
+          <t>0.08228699551569504 +/- 0.006462675030660199</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.01156310057655351 +/- 0.002654690278666668</t>
+          <t>-0.01153106982703398 +/- 0.002649080477659862</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -4026,72 +4026,72 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>0.0016763599042079803 +/- 0.0007718449656297268</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.017618884707492323 +/- 0.004600769136338501</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.017550461854259312 +/- 0.00231553489688917</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.017550461854259312 +/- 0.00231553489688917</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.030345535408826542 +/- 0.002201525903961151</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-0.023811152925077007 +/- 0.0035328992523915334</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-0.024290112897707862 +/- 0.002680744170257914</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>-0.008655490933971966 +/- 0.0034587396995894018</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.016079370509750224 +/- 0.0023454172426962245</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-0.008210742387957614 +/- 0.0028623333100721046</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.15795415668833387 +/- 0.005376856580452677</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.020218953130345507 +/- 0.0022972660915770984</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.1858706808073896 +/- 0.0052912812958745385</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>0.001710571330824473 +/- 0.0007801405577140845</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-0.017618884707492323 +/- 0.004600769136338501</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.017550461854259312 +/- 0.00231553489688917</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.017550461854259312 +/- 0.00231553489688917</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.030345535408826542 +/- 0.002201525903961151</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-0.023811152925077007 +/- 0.0035328992523915334</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-0.024290112897707862 +/- 0.002680744170257914</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-0.008655490933971966 +/- 0.0034587396995894018</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.016079370509750224 +/- 0.0023454172426962245</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-0.008176530961341123 +/- 0.0028723340059599567</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.15795415668833387 +/- 0.005376856580452677</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0.020218953130345507 +/- 0.0022972660915770984</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0.1858706808073896 +/- 0.0052912812958745385</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0.0016763599042079803 +/- 0.0007718449656297268</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.03367909238249599 +/- 0.0024189864773815867</t>
+          <t>-0.03367909238249598 +/- 0.002479052033063059</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.025672609400324186 +/- 0.0027611720504436936</t>
+          <t>-0.025607779578606195 +/- 0.002750496393594354</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.01782820097244737 +/- 0.002765734717368109</t>
+          <t>-0.017860615883306376 +/- 0.002702128433888793</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.003577183370931303 +/- 0.001063486948114711</t>
+          <t>0.0036094102481468936 +/- 0.0011051516725415313</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.005091846600064409 +/- 0.0020011826872394535</t>
+          <t>0.005059619722848807 +/- 0.0020333601745855527</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
